--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -12,20 +12,29 @@
       <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="1">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -43,9 +52,9 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="72" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="74" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -66,7 +75,7 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>codex/experimental-features</t>
+          <t>experimental-features</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
@@ -98,7 +107,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shared stable UI: octopus mark, black canvas, depth, TTV, RunTime, ascent gauge, stopwatch.</t>
+          <t>Octopus mark, black canvas, depth, TTV, RunTime, ascent gauge, stopwatch.</t>
         </is>
       </c>
     </row>
@@ -503,7 +512,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docs/EXPERIMENTAL_FEATURES.md and Buddy preview only in experimental.</t>
+          <t>EXPERIMENTAL_FEATURES.md and Buddy preview only in experimental.</t>
         </is>
       </c>
     </row>
@@ -530,7 +539,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lives on branch main-iOS, not in main or codex/experimental-features.</t>
+          <t>Lives on branch main-iOS, not in main or experimental-features.</t>
         </is>
       </c>
     </row>

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -221,7 +221,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>main-iOS e863de7</t>
+          <t>main-iOS afcab8e</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -133,10 +133,10 @@
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="76" customWidth="1"/>
+    <col min="3" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="78" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -170,6 +170,11 @@
           <t/>
         </is>
       </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -202,34 +207,44 @@
           <t/>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Branch commits</t>
+          <t>Compared branches</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>main da4541f</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>experimental-features 3fe5ec4</t>
+          <t>codex/experimental-features</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>main-iOS afcab8e</t>
+          <t>main-iOS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t/>
+          <t>codex/ios-experimental-features</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -238,27 +253,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t/>
+          <t>Reference commits</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>main c3af69b</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>watch experimental 3fe5ec4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>main-iOS afcab8e</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>iOS experimental 39cfa20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -266,68 +281,83 @@
           <t/>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr" s="2">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="2">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="2">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="2">
+      <c r="D6" t="inlineStr" s="2">
         <is>
           <t>codex/experimental-features</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr" s="2">
+      <c r="E6" t="inlineStr" s="2">
         <is>
           <t>main-iOS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr" s="2">
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Apple Watch app</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>watchOS app lives in main and experimental-features.</t>
         </is>
       </c>
     </row>
@@ -339,59 +369,69 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iPhone companion app</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>iOS companion app lives only in main-iOS.</t>
+          <t>Apple Watch app</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>watchOS app lives in main and Watch experimental.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Watch premium dive-computer look and feel</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Black canvas, thin technical panels, octopus mark, large depth, colored ascent gauge.</t>
+          <t>iPhone companion app</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>iOS app lives in main-iOS and iOS experimental.</t>
         </is>
       </c>
     </row>
@@ -403,59 +443,69 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iOS companion premium mockup look and feel</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dark cyan iPhone UI aligned to the supplied iOS mockup.</t>
+          <t>Watch premium dive-computer look and feel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Black canvas, octopus mark, large depth, technical panels.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dive Core</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Apple water submersion API scaffold</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Entitlement still pending for production depth data.</t>
+          <t>iOS companion premium dark cyan look and feel</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>iOS companion follows supplied iPhone mockup style.</t>
         </is>
       </c>
     </row>
@@ -467,7 +517,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Current/max/average depth, temperature, runtime, TTV</t>
+          <t>Apple water submersion API scaffold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="3">
@@ -480,14 +530,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr" s="5">
-        <is>
-          <t>Display/reference only</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Core live metrics are watchOS features.</t>
+      <c r="E11" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Entitlement still pending for production depth data.</t>
         </is>
       </c>
     </row>
@@ -499,7 +554,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manual stopwatch controls</t>
+          <t>Current/max/average depth, temperature, runtime, TTV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="3">
@@ -512,14 +567,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>START, STOP, RESET on Apple Watch.</t>
+      <c r="E12" t="inlineStr" s="5">
+        <is>
+          <t>Display/reference only</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="5">
+        <is>
+          <t>Display/reference only</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Core live metrics are watchOS runtime features.</t>
         </is>
       </c>
     </row>
@@ -531,7 +591,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ascent-rate gauge</t>
+          <t>Manual stopwatch controls</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="3">
@@ -544,14 +604,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr" s="5">
-        <is>
-          <t>Planner/reference only</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Watch live gauge uses green/yellow/red zones.</t>
+      <c r="E13" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>START, STOP, RESET on Apple Watch.</t>
         </is>
       </c>
     </row>
@@ -563,7 +628,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>User-configurable ascent-rate limits</t>
+          <t>Ascent-rate gauge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="3">
@@ -576,26 +641,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Stored locally via UserDefaults on watchOS.</t>
+      <c r="E14" t="inlineStr" s="5">
+        <is>
+          <t>Planner/reference only</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="5">
+        <is>
+          <t>Planner/reference only</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Watch live gauge uses green/yellow/red zones.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Dive Core</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Compass screen and bearing controls</t>
+          <t>User-configurable ascent-rate limits</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="3">
@@ -613,21 +683,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CoreLocation heading with SET/CLEAR bearing.</t>
+      <c r="F15" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Stored locally on watchOS.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Local dive log persistence</t>
+          <t>Compass screen and bearing controls</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="3">
@@ -640,14 +715,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Watch and iOS maintain local log models.</t>
+      <c r="E16" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="5">
+        <is>
+          <t>Buddy companion view only</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>iOS experimental mirrors plausible direction status only.</t>
         </is>
       </c>
     </row>
@@ -659,7 +739,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dive detail and profile chart</t>
+          <t>Local dive log persistence</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="3">
@@ -677,9 +757,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>iOS has richer companion detail views.</t>
+      <c r="F17" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Watch and iOS maintain local log models.</t>
         </is>
       </c>
     </row>
@@ -691,7 +776,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPS entry/exit metadata</t>
+          <t>Dive detail and profile chart</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="3">
@@ -709,21 +794,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Watch captures; iOS model displays/exports where available.</t>
+      <c r="F18" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>iOS has richer companion detail views.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Subsurface CSV export</t>
+          <t>GPS entry/exit metadata</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="3">
@@ -741,21 +831,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CSV export service exists on watch and iOS companion.</t>
+      <c r="F19" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Watch captures; iOS displays/exports where available.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bundled user images/checklists screen</t>
+          <t>Subsurface CSV export</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="3">
@@ -768,31 +863,36 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Watch-only bundled image viewer.</t>
+      <c r="E20" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CSV export service exists on watch and iOS companion.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Buddy Assist preset messaging</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
+          <t>Bundled user images/checklists screen</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="3">
@@ -805,21 +905,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Must remain isolated from main.</t>
+      <c r="F21" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Watch-only bundled image viewer.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Experimental Watch</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Buddy Link proximity indicator</t>
+          <t>Buddy Assist preset messaging</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="4">
@@ -837,21 +942,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>RSSI ping every 15 seconds with green/yellow/red status.</t>
+      <c r="F22" t="inlineStr" s="5">
+        <is>
+          <t>Companion preparation only</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Actual Buddy message runtime remains Watch experimental.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Experimental Watch</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Received Buddy message banner and answer flow</t>
+          <t>Buddy Link proximity indicator</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="4">
@@ -869,21 +979,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ANSWER uses the same preset message set.</t>
+      <c r="F23" t="inlineStr" s="5">
+        <is>
+          <t>Companion status only</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Watch experimental uses RSSI ping every 15 seconds.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Experimental Watch</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Buddy compass plausible direction block</t>
+          <t>Received Buddy message banner and answer flow</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="4">
@@ -901,21 +1016,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Heading, shared bearing, last known direction.</t>
+      <c r="F24" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ANSWER flow is Watch-side runtime.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Experimental Watch</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Secure pre-dive Buddy pairing</t>
+          <t>Buddy compass plausible direction block</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="4">
@@ -933,9 +1053,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Pairing locked during active dive; TRUST requires matching confirmation code.</t>
+      <c r="F25" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>iOS experimental mirrors heading/shared bearing/plausible direction.</t>
         </is>
       </c>
     </row>
@@ -947,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Keychain-backed Buddy authentication material</t>
+          <t>Secure pre-dive Buddy pairing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="4">
@@ -965,9 +1090,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SecureBuddyStore stores trusted buddy key in Keychain.</t>
+      <c r="F26" t="inlineStr" s="5">
+        <is>
+          <t>Companion review only</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>iOS experimental shows VERIFY/TRUSTED status, code and fingerprint.</t>
         </is>
       </c>
     </row>
@@ -979,7 +1109,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Authenticated Buddy message envelope</t>
+          <t>Keychain-backed Buddy authentication material</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="4">
@@ -997,21 +1127,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>HMAC-SHA256 with session, timestamp, sequence, replay rejection.</t>
+      <c r="F27" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Keychain Buddy runtime remains Watch experimental only.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Frameworks</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CoreBluetooth dependency</t>
+          <t>Authenticated Buddy message envelope</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="4">
@@ -1029,9 +1164,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Only experimental-features has BLE scaffolding.</t>
+      <c r="F28" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HMAC-SHA256 message envelope remains Watch experimental runtime.</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1183,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Security.framework dependency</t>
+          <t>CoreBluetooth dependency</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="4">
@@ -1061,21 +1201,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Only experimental-features needs Keychain for Buddy keys.</t>
+      <c r="F29" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BLE scaffolding exists only in Watch experimental.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iOS Companion</t>
+          <t>Frameworks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Logbook screen</t>
+          <t>Security.framework dependency</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="4">
@@ -1083,31 +1228,36 @@
           <t>No</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr" s="4">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>iPhone companion logbook UI.</t>
+      <c r="D30" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Only Watch experimental needs Keychain for Buddy keys.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iOS Companion</t>
+          <t>Frameworks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dive analytics screen</t>
+          <t>WatchConnectivity dependency</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="4">
@@ -1125,9 +1275,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Advanced statistics and charts.</t>
+      <c r="F31" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>iOS companion uses WatchConnectivity scaffold.</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1294,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dive planner with Buhlmann ZH-L16C</t>
+          <t>Logbook screen</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="4">
@@ -1157,9 +1312,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Planner branch contains Buhlmann planning services.</t>
+      <c r="F32" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>iPhone companion logbook UI.</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gas/MOD/decompression planning UI</t>
+          <t>Dive analytics screen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="4">
@@ -1189,9 +1349,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Planning model and gas plan views.</t>
+      <c r="F33" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Advanced statistics and charts.</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1368,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WatchConnectivity sync scaffold</t>
+          <t>Dive planner with Buhlmann ZH-L16C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="4">
@@ -1221,9 +1386,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>WatchSyncService activates WCSession.</t>
+      <c r="F34" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Planner services live in iOS branches.</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1405,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cloud backup section</t>
+          <t>Gas/MOD/decompression planning UI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="4">
@@ -1248,83 +1418,357 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr" s="5">
-        <is>
-          <t>Prepared</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>UI indicates iCloud sync prepared / backup to enable.</t>
+      <c r="E35" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Planning model and gas plan views.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>iOS Companion</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Buddy/BLE excluded from main</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr" s="6">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr" s="6">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>main has no BuddyAssist/SecureBuddy files and no CoreBluetooth/Security dependencies.</t>
+          <t>Equipment screen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>iOS companion equipment view.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Buddy Lab tab</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Premium iOS experimental companion surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Secure pairing review UI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VERIFY/TRUSTED, confirmation code, fingerprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Buddy Link status UI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ONLINE/LOST, signal color, RSSI, ping context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Preset message preparation UI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Same message set as Watch experimental, no direct BLE send.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Watch experimental sync notes</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Documents runtime boundary between iOS companion and Watch BLE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Buddy/BLE excluded from main</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="6">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="6">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="6">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>main has no BuddyAssist/SecureBuddy files and no BLE dependencies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Buddy/BLE runtime excluded from iOS stable</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="6">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="6">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="6">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>main-iOS remains stable companion without Buddy Lab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Experimental features not production safety systems</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr" s="6">
+      <c r="C44" t="inlineStr" s="6">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="3">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr" s="6">
+      <c r="D44" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="6">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Docs keep Buddy Assist and RSSI proximity marked experimental.</t>
+      <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Docs keep Buddy and RSSI proximity marked experimental.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F37"/>
+  <autoFilter ref="A6:G44"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -263,7 +263,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>watch experimental 3fe5ec4</t>
+          <t>watch experimental 9c0ac8e</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -273,7 +273,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>iOS experimental 39cfa20</t>
+          <t>iOS experimental 0207303</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -273,7 +273,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>iOS experimental 0207303</t>
+          <t>iOS experimental d726e24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -258,7 +258,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main c3af69b</t>
+          <t>main ccfea3f</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>iOS experimental d726e24</t>
+          <t>iOS experimental 0300730</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1767,8 +1767,45 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Experimental preview screenshots</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Static premium UI previews stored under Docs/iOS/FeatureScreenshots.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:G44"/>
+  <autoFilter ref="A6:G45"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -258,12 +258,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main ccfea3f</t>
+          <t>main a766224</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>watch experimental 9c0ac8e</t>
+          <t>watch experimental 2ac26c8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -184,7 +184,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main a766224</t>
+          <t>main a766224 + matrix 85d227a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>watch experimental 2ac26c8</t>
+          <t>watch experimental e6b02f7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>iOS experimental 0300730</t>
+          <t>iOS experimental a2ddbfa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1804,8 +1804,193 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Experimental Watch</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pre-water mode selector: Diving / Apnea / Snorkeling</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Implemented only in Watch experimental as ModeSelectionView and ExplorationStore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Experimental Watch</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Snorkeling runtime, waypoint nav, return-to-entry, GPS markers</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="5">
+        <is>
+          <t>Companion planning only</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Watch runtime UI plus companion route planning support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Experimental Watch</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Apnea timer, recovery assistant, dive counter, warning layer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="5">
+        <is>
+          <t>Analytics/planning only</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Watch runtime UI plus iOS analytics companion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Explore tab: snorkeling map, route, waypoint planner</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Premium iOS companion surface, MapLibre/OpenSeaMap-ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>iOS Experimental</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Apnea analytics, readiness, fatigue, recovery, export GPX/CSV</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Implemented in ExplorationCenterView and ExplorationPlanningStore.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:G45"/>
+  <autoFilter ref="A6:G50"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -258,12 +258,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main a766224 + matrix 85d227a</t>
+          <t>main 34db54a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>watch experimental e6b02f7</t>
+          <t>watch experimental 8d15a93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -184,7 +184,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main 34db54a</t>
+          <t>main de30f24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>watch experimental 8d15a93</t>
+          <t>watch experimental 75ecbcc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>main-iOS afcab8e</t>
+          <t>main-iOS dfe8985</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>iOS experimental a2ddbfa</t>
+          <t>iOS experimental 41fc6f5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1989,8 +1989,156 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>iCloud KVS mirror for Watch dive logs</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Watch logs saved locally and mirrored to iCloud when capability is enabled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>iCloud KVS mirror for Watch ascent/exploration settings</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="5">
+        <is>
+          <t>Ascent only</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="3">
+        <is>
+          <t>Ascent + exploration</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Experimental also mirrors Snorkeling/Apnea state; Buddy keys remain Keychain-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>iCloud KVS mirror for iOS logbook and planner</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>iOS stores logbook sessions and planner inputs locally plus iCloud mirror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>iCloud KVS mirror for iOS experimental Buddy/Explore state</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="4">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Experimental iOS persists Buddy Lab, Explore route, waypoint, warning and sync/export state.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:G50"/>
+  <autoFilter ref="A6:G54"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>main 2c2d335</t>
+          <t>main 9077699</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>watch experimental cd71cc8</t>
+          <t>watch experimental da1f9b3</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>iOS experimental 7e06f59</t>
+          <t>iOS experimental 476071a</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr"/>

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>main 9077699</t>
+          <t>main acbafc5</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>watch experimental da1f9b3</t>
+          <t>watch experimental ff00a92</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr"/>
@@ -563,22 +563,22 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>main acbafc5</t>
+          <t>main dc916a3</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>watch experimental ff00a92</t>
+          <t>watch experimental 1ece23f</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>main-iOS dfe8985</t>
+          <t>main-iOS 6ad130c</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>iOS experimental 476071a</t>
+          <t>iOS experimental 937b261</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr"/>

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>main dc916a3</t>
+          <t>main 83f2857</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>watch experimental 1ece23f</t>
+          <t>watch experimental d2019f7</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>iOS experimental 937b261</t>
+          <t>iOS experimental f0e6ffb</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr"/>

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>main 83f2857</t>
+          <t>main 48b81db</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>main-iOS 6ad130c</t>
+          <t>main-iOS cb8cbd2</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>iOS experimental f0e6ffb</t>
+          <t>iOS experimental f32fe30</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr"/>

--- a/Docs/Branch_Functionality_Matrix.xlsx
+++ b/Docs/Branch_Functionality_Matrix.xlsx
@@ -3,10 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix Current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature Matrix'!$A$6:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature Matrix Current'!$A$1:$J$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Matrix'!$A$6:$G$54</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -14,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Aptos"/>
       <sz val="11"/>
@@ -36,8 +39,15 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000151C"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -74,8 +84,28 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000DDEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -98,11 +128,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="0025323A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -123,6 +158,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,6 +543,9345 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J189"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="7" min="1" max="1"/>
+    <col width="28" customWidth="1" style="7" min="2" max="2"/>
+    <col width="22" customWidth="1" style="7" min="3" max="3"/>
+    <col width="18" customWidth="1" style="7" min="4" max="4"/>
+    <col width="34" customWidth="1" style="7" min="5" max="5"/>
+    <col width="16" customWidth="1" style="7" min="6" max="6"/>
+    <col width="64" customWidth="1" style="7" min="7" max="7"/>
+    <col width="38" customWidth="1" style="7" min="8" max="8"/>
+    <col width="58" customWidth="1" style="7" min="9" max="9"/>
+    <col width="28" customWidth="1" style="7" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>UI Reference</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>internationalization &amp; languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Live dive computer</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Schermata primaria con profondita attuale, TTV, RunTime, gauge risalita, cronometro e START/STOP/RESET.</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Stabile; preservare logica immersione, calcoli e warning.</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>GPS inizio/fine immersione</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Registra punti GPS di superficie a inizio e fine immersione con best-effort fix.</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>gps_start_wait_from_workflow.png; gps_end_registered_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>GPS non affidabile sott'acqua; solo metadata di superficie.</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Avviso risalita (banner inline)</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Banner rosso non bloccante tra TTV/RunTime e profondita; gauge, depth, cronometro e controlli restano visibili; haptic first+repeat ~1.75 s.</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>ascent_alarm.png; ascent_warning_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Policy: Docs/WATCH_MAIN_UX_CONVENTIONS.md; codice AscentWarningBannerView. Soglie/algoritmi risalita invariati.</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>it, en: ascent_alarm_title, ascent_alarm_instruction, ascent_alarm_speed_unit, ascent_alarm_accessibility_hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Bussola</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Bussola dedicata con heading, SET BEARING, CLEAR e stato permessi/disponibilita.</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>compass_in_dive_CORRECT_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Terminologia UI: BUSSOLA quando richiesto; nessuna promessa di tasto laterale non gestito.</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Log immersioni</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Lista immersioni, dettaglio, coordinate reali quando disponibili, delete e export CSV ultimo/dettaglio.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>dive_log_from_workflow.png; dive_detail_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Mantiene ultime sessioni e sync iCloud/WatchConnectivity dove disponibile.</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Export Subsurface</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>CSV importabile in flusso Subsurface con profondita, temperatura e coordinate; feedback export/share su detail e ultima immersione.</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>export_subsurface_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Formato CSV documentato in Docs/iOS/SUBSURFACE_EXPORT.md.</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Image viewer</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Browser immagini/checklist statiche bundle.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>image_browser_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Caricamento da Resources/UserImages.</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Impostazioni, allarmi, info batteria</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Settings raggiungibile con limiti risalita, allarmi persistenti, haptic on/off, stato GPS, stato sensore profondita, sync, device e batteria reale.</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>settings_from_workflow.png; alarms_from_workflow.png; info_battery_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Le unita restano metriche fisse; schermo/Always On gestiti da watchOS.</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Stable main gating</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>La navigazione main espone solo Diving, bussola, settings, immagini e log; Apnea/Snorkeling/Buddy restano experimental.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Previene dipendenze UI production da superfici sperimentali.</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>GPS confirmation screens</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Le conferme punto inizio/fine sono mostrate dal lifecycle immersione e usano stato non disponibile se manca il fix.</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>gps_start_wait_from_workflow.png; gps_end_registered_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Nessuna coordinata finta su sessioni senza GPS.</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling Live</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Runtime, distanza, velocita media, profondita attuale, GPS, waypoint, ritorno e marcatori.</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>01_snorkeling_live_final.png</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>UI sperimentale; riusa ExplorationStore e GPSManager.</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Mappa Waypoint</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Mappa leggera SwiftUI con griglia marina, rotta tratteggiata gialla, marker corrente e waypoint.</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>02_Mappa_Waypoint_reference.png</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Nessun tile online su Watch; TODO per MBTiles/sync iOS.</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Mappa Ritorno</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Mappa leggera SwiftUI per ritorno al punto di partenza con rotta ciano e home marker.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>03_Mappa_Ritorno_reference.png</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Separata da Mappa Waypoint.</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Direzione Waypoint</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Dial stile bussola che mostra bearing verso waypoint, non bussola generica.</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>04_Direzione_Waypoint_reference.png</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Non cambia algoritmi bussola.</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Log Marcatori POI</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Lista POI/marker snorkeling raggiungibile da settings/live flow con stato arricchimento iPhone e tap verso dettaglio.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>05_Log_Marcatori_POI_AppleWatch_reference.png</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Watch-sized UI; dati da ExplorationStore.</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Dettaglio Marcatore POI</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Dettaglio POI con ora, distanza, direzione, profondita, temperatura, waypoint, session id e stato Da arricchire su iPhone.</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>06_Dettaglio_Marcatore_POI_AppleWatch_reference.png</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Watch non modifica foto/commenti; sync iOS resta TODO esplicito.</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>GPS Marker confirmation</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Conferma marker salvato con check verde, haptic, coordinate o GPS non disponibile, link a log/dettaglio.</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>gps_marker_style_reference.png</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Payload leggero include timestamp/GPS/profondita/temperatura/bearing/waypoint/sessione quando disponibili.</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Allarmi Snorkeling</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Soglie snorkeling modificabili e persistite localmente via AppStorage: profondita, tempo, distanza, batteria.</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>08_Allarmi_Snorkeling_reference.png</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Store dedicato e sync settings restano TODO.</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Apnea assistant</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Timer apnea, recovery assistant, counter, warning e blocco bussola.</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Training aid; non sostituisce procedure buddy.</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Apnea menu e session type</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Menu Apnea con Sessione, Tabelle, Statistiche, Logbook e selezione Acque Libere.</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_02_03</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Dinamica, Statica e Personalizzata sono placeholder disabilitati.</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Open-water configuration</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Configurazione per allarmi, intervallo superficie e profondita massima con valori persistiti localmente via AppStorage.</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_04</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Modello Apnea dedicato e sync settings restano TODO.</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Countdown e surface waiting</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Countdown automatico 03/02/01 VAI, tap manuale e haptic tick/start prima della sessione superficie.</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_05_06</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Non modifica algoritmi profondita o risalita.</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Session lifecycle</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Avvio automatico immersione da profondita, chiusura al ritorno in superficie e recovery timer.</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_07_12</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Usa ExplorationStore esistente; non modifica algoritmi profondita o risalita.</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Summary, profile, details, save</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Riepilogo, grafico, dettagli e conferma salvataggio per la sessione Apnea.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_13_16</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Durata e max depth reali se presenti; profilo, HR, temperatura e medie sono TODO.</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Logbook e statistiche Apnea</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Lista e statistiche Apnea con record recente e metriche aggregate parziali.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_17_18</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Storico completo e aggregati restano TODO finche il modello non espone i dati.</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Buddy Assist</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Buddy pairing/messages</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Pairing pre-dive, messaggi preset, Buddy Link, proximity e HMAC envelope.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>SecureBuddyPairingMockup.svg</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Limitazioni watchOS BLE documentate.</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Logbook companion</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Logbook iOS premium con titolo, ricerca scura, stacked dive cards, thumbnail e tabbar attiva ciano.</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>ios_logbook_reference.png; iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Branch iOS stabile; allineamento UI-only, sync WatchConnectivity invariato.</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Dive detail companion</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Dettaglio immersione con tab riepilogo/grafici/dettagli, immagine sito, griglia metriche, grafico profondita ciano, gas card ed export.</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>ios_dive_detail_reference.png; iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>UI-only; export, modelli e dati immersione invariati.</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Planner iOS input</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Planner con titolo, disclaimer in-app, controllo segmentato modalita, profilo immersione, gas cards con bordi neon e pulsante ciano Calcola Piano.</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>ios_planner_reference.png; iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Calcoli/store/binding invariati; disclaimer obbligatorio per output semplificato.</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Planner result iOS</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Risultato piano con tab PIANO/CURVA BUHLMANN/GRAFICI che mostrano contenuti distinti, griglia riepilogo, tabella risalita e curva Bühlmann.</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>ios_plan_result_reference.png; iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Riusa store.plan, store.input e store.buhlmann.curve; output non certificato.</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Settings iOS</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Tab Settings con onboarding operativo, preferenze locali unita/export, Watch sync retry, conflitti Watch, iCloud/manual sync, demo logbook e note Subsurface.</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Settings sync e indicato locale-only; cloud KVS non promette conflict resolver completo.</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Stable tab set</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Tabbar stable su main workspace: Logbook, Analisi, Planner, Attrezzatura, Altro (italiano); route GPS riassunta in Analisi.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png; Docs/ReferenceUI/iOS_Companion_reference.png</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Storico: branch `main-iOS` poteva elencare Route Review separata; allineare descrizioni al main corrente.</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Explore/Snorkeling planning</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Pianificazione waypoint, route mock, stato cache offline e sync verso Watch.</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>MapLibre/OpenSeaMap-ready UI; niente dipendenza nuova in questo pass.</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Apnea Review</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Card companion Apnea Review con tab interattivi Riepilogo/Grafico/Dettagli, profilo mock e metriche riepilogo.</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Metriche sincronizzate da Watch non ancora cablate; placeholder espliciti.</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>POI enrichment</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Superficie raggiungibile per foto, video, commenti, categorie, tag e note specie con stato media mock/TODO.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>06_Dettaglio_Marcatore_POI_AppleWatch_reference.png</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Watch crea payload leggero; media upload/save reale non implementato.</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Roadmap</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Offline maps MBTiles</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Base OSM compatibile, overlay OpenSeaMap opzionale, futuri GEBCO/EMODnet.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>02_Mappa_Waypoint_reference.png</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Non usare tile server pubblici hard-coded in produzione.</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling settings</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Settings Snorkeling raggiungibili con Log Marcatori, Allarmi, Calibrazione Bussola, Legenda Icone Mappe e toggle haptic sperimentale.</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Non include unita globali o info app.</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>Watch -&gt; iPhone POI sync boundary</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>UI dichiara payload POI locale pronto e sync WatchConnectivity reale non ancora implementato.</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>05_Log_Marcatori_POI_AppleWatch_reference.png</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Richiede queue offline, duplicate prevention e conferma ricezione iPhone.</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Apnea</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Watch -&gt; iPhone Apnea sync boundary</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Conferma salvataggio mostra boundary per inviare durata, max depth e recovery a iPhone.</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_16</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Profilo campioni reale non disponibile in questo pass.</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>iPhone -&gt; Watch route/settings manifest</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>UI-only</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Explore Lab prepara manifest mock per waypoint, route e settings senza invio Watch reale.</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>WatchConnectivity payload completo, offline queue e duplicate prevention restano TODO.</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Maps</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Offline map readiness</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>UI mostra stato MBTiles/MapLibre/OpenStreetMap/OpenSeaMap/GEBCO/EMODnet come roadmap esplicita.</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Nessun nuovo motore mappe o dipendenza introdotta.</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Experimental settings navigation</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Settings, Allarmi, Limiti Risalita e Info sono raggiungibili dalla navigazione experimental con preferenze locali persistenti.</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Non modifica logica GPS, bussola, depth o ascent.</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Unavailable sensor states</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>Profondita non disponibile mostra --; Apnea usa HR OFF, BAT -- e TEMP -- invece di valori finti.</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_07_12</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Serve cablaggio futuro HealthKit/batteria/temperatura Apnea reale.</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Buddy Assist</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Lab-only safety gate</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>Buddy Assist resta visibile ma disabilitato/lab-only finche il relay BLE Watch non e validato.</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>SecureBuddyPairingMockup.svg</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Evita false promesse safety o messaggistica underwater production.</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Experimental sync queue status</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>POI e record Apnea usano contratto lightweight con ultimo payload, stato delivery e conteggio coda visibili.</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>APNEA_WORKFLOW_16</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>ACK/retry persistente, duplicate prevention e merge iOS restano roadmap.</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Planner</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>Planner lab safety gate</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Plan Result mostra PIANO LAB ed EXPORT LAB per separare output informativo da piano operativo certificato.</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>ios_plan_result_reference.png</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Nessuna modifica ai calcoli planner.</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Dead affordance cleanup</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Logbook add/overflow e Dive Detail edit/ellipsis non appaiono piu come azioni reali non cablate.</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Preferisce label LAB/OFF e feedback testuale.</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Experimental settings center</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>More espone preferenze locali per unita, CSV export, diagnostica Watch Sync e gate safety mock.</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Notifiche, permessi media e sync production restano roadmap.</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Experimental import/queue UX</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Explore Lab mostra queue route/settings; More mostra conteggio/status import experimental ricevuti dal Watch.</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Queue persistente production, ACK, retry e merge non completi.</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>Alarm thresholds</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Soglie allarme profondita, tempo e batteria sono editabili, persistite e applicate dal motore immersione MAIN.</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>alarms_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>Non modifica algoritmi profondita/risalita; aggiorna solo soglie configurabili.</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Haptics</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>Stopwatch haptics</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>START, STOP e RESET cronometro producono feedback haptic rispettando il toggle haptics Watch.</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>Toni audio non usati sott'acqua; settings dichiara feedback via vibrazione.</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>Experimental source exclusion</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>project.yml esclude Apnea, Snorkeling, Buddy Assist e concept experimental dal target membership MAIN.</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>project.yml</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Da verificare con xcodegen generate su macOS.</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Bluetooth claim removed</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>Watch MAIN non include piu la privacy string Bluetooth Buddy perche Buddy Assist non e una funzione production visibile.</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>App/Info.plist</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>La privacy string resta appropriata solo sui rami dove Buddy/BLE e target-included.</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>Logbook importa CSV compatibili con time_seconds, depth_m, temperature_c e coordinate entry/exit opzionali.</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Validazione device e file edge cases ancora richiesta.</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>Route Review</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>Route calcolate dai punti GPS surface-only entry/exit dei log importati o sincronizzati.</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Non e un motore mappa production; non promette tracking subacqueo. Su repository unificato `main` la stessa funzione e nella tab **Analisi** (nessuna tab Explore su MAIN).</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>Metriche logbook reali, SAC medio, distribuzione gas e riepilogo route GPS.</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>Nessun analytics engine AI o placeholder main.</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>Equipment profile</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>Profilo attrezzatura persistente con checklist e SAC pianificazione.</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Multi-profilo e sync Watch restano roadmap.</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Watch conflicts</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Conflitti Watch import vengono salvati e risolti manualmente da Settings.</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Utente puo mantenere locale o usare payload Watch.</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>KVS delete tombstones</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>Eliminazioni log iOS registrano tombstone locali/KVS per ridurre riapparizione dei record cancellati.</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Policy cloud completa ancora semplice e da validare su device.</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Planner</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic warnings</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>Planner mostra warning dinamici per modello semplificato, MOD e sufficienza gas.</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>ios_plan_result_reference.png</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Non certificato; non sostituisce strumenti validati.</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>MAIN UX audit report</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>Report pre-modifica MAIN per reachability, navigation, settings, hardware interactions, blockers e safety.</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_BRANCHES_UX_INTERACTION_AUDIT_20260517_CURRENT_PRE_MODIFICATION.docx</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Documento generato senza modificare runtime code.</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>MAIN iOS UX audit coverage</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>Audit companion MAIN su tabbar, settings, planner, sync, export/import, empty states e accessibility risks.</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_BRANCHES_UX_INTERACTION_AUDIT_20260517_CURRENT_PRE_MODIFICATION.docx</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Applicare eventuali fix in commit separati dalla documentazione.</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>Watch sync key helper isolation</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>Verificare su macOS che `WatchSyncAuth` MAIN non dipenda da helper Buddy esclusi dal target MAIN.</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>project.yml; WatchSyncAuth.swift</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Non corretto in questo pass per rispettare scope docs-only.</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>App icon PNG presence</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>Verificare che tutti i PNG referenziati da AppIcon.appiconset siano presenti nel branch iOS MAIN prima del release build.</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>AppIcon.appiconset/Contents.json</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Asset/config, non runtime logic; richiede validazione Xcode.</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Action Button and App Intents discoverability</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Documentare in UI o help che START/STOP/RESET sono disponibili via controlli e App Intents quando watchOS li espone.</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>ToggleStopwatchIntent; ResetStopwatchIntent</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Apple non espone callback arbitrari per tasto laterale/watchOS app.</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Editable settings completion</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>Completare o marcare esplicitamente read-only le preferenze iOS ancora informative/local-only.</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>Non cambiare sync/persistence senza contratto prodotto.</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Logbook</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Destructive confirmations and empty states</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>Aggiungere conferme delete/reset e empty state piu chiari per logbook/import/export dove mancano.</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>Da implementare in pass runtime separato.</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>macOS XcodeGen and xcodebuild validation</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>Eseguire `xcodegen generate` e build target Watch/iOS su macOS dopo ogni merge branch-wide.</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>project.yml</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>Ambiente Windows non puo validare SDK Apple.</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Shortcut and manual lifecycle help</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Settings MAIN spiega App Intents/shortcut, limiti watchOS del tasto laterale, avvio manuale e stato local-only delle impostazioni.</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Copy/UI only; nessuna modifica a GPS, bussola, profondita o state machine immersione.</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Logbook</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Empty logbook and delete confirmation</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>Il logbook Watch mostra stato vuoto, export disabilitato senza primo log e conferma distruttiva prima di eliminare una sessione.</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Preserva modello log esistente.</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Glove-friendly alarm controls</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Soglie allarme Watch scrollabili, etichettate come locali e con controlli +/- piu grandi per uso con guanti.</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>alarms_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>Non cambia calcoli profondita/tempo/batteria; solo affordance e layout.</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Read-only/local-only settings clarity</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Settings iOS marca unita/export come non editabili o local-only, chiarisce permessi notifiche e allarmi gestiti su Watch.</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>Sync settings bidirezionale resta roadmap.</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Empty states</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>Logbook, Route Review e Analysis mostrano empty state guidati quando non esistono immersioni, route GPS o statistiche disponibili.</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Non crea dati finti; invita a sync Watch o import CSV.</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Destructive confirmations</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Delete immersione e reset profilo attrezzatura richiedono conferma prima di modificare dati utente.</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Conferme UI; persistenza esistente invariata.</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>WatchSyncAuth MAIN isolation</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>WatchSyncAuth usa generazione random stabile con Security/SecRandomCopyBytes e non dipende da SecureBuddyStore escluso dal target MAIN.</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>project.yml; WatchSyncAuth.swift</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>Fix build blocker MAIN; Buddy/BLE resta experimental.</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>Signing</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Depth entitlement</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Config Watch include com.apple.developer.coremotion.water-submersion ed e collegata da project.yml; validazione Apple portal/device resta obbligatoria.</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Config/DIRDiving.entitlements; App/Info.plist</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Non dichiarare validazione device finche non viene eseguita su Apple Watch Ultra reale.</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr"/>
+      <c r="J77" s="9" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>GPS no-fix truthfulness</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Conferme GPS distinguono punto registrato, ultimo punto noto usato e GPS non disponibile/punto non registrato.</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>gps_start_wait_from_workflow.png; gps_end_registered_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>GPS resta surface-only; nessuna coordinata finta.</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Ascent warning live context</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Banner inline mantiene TTV, RunTime, profondita, gauge risalita, cronometro e controlli visibili durante l'allarme.</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>ascent_alarm.png</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20: non full-screen; vedi WATCH_MAIN_UX_CONVENTIONS.md.</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>it, en ascent_alarm_*</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Haptics-off dive visibility</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Live dive mostra APTICA DISATTIVATA e AVVISI SOLO VISIVI quando haptics e off, mantenendo warning visuali.</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>Non forza haptic se l'utente lo disattiva.</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Watch sync trust hardening</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Payload Watch senza peer secret verificata sono non fidati e visibili come Associazione Watch non verificata.</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>Nessuna fallback key deterministica concede trust silenzioso.</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr"/>
+      <c r="J81" s="9" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Local/cloud merge independence</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>DiveLogStore legge local e cloud separatamente prima del merge e mantiene tombstone delete espliciti.</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>Policy conflict cloud completa richiede ancora QA multi-device.</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>CSV import robustness</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Import CSV preserva data sorgente quando presente, usa hash deterministico anti-duplicato e mostra feedback import/duplicati/errori.</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>Testare file valido, re-import, righe vuote e CSV malformed.</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr"/>
+      <c r="J83" s="9" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Explore empty-state actions</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Route Review empty state usa pulsanti reali per sync, import CSV e impostazioni.</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>Azioni non implementate non devono apparire come bottoni.</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Planner modes and acknowledgement</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>Planner MAIN espone Semplice come modalita comportamentale attiva, marca Avanzato/Tecnico planned, valida input e richiede acknowledgement safety.</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>ios_planner_reference.png</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>Non cambia calcoli planner/decompressione.</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr"/>
+      <c r="J85" s="9" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Unit conversion decision</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Unita iOS restano mantenute: conversione display-only coerente per profondita, temperatura, distanza e SAC.</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>Dati salvati, planner, import/export CSV e sync Watch restano metrici.</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr"/>
+      <c r="J86" s="9" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Logbook</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>Visible detail delete</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>DiveDetailView espone un pulsante rosso ELIMINA LOG con conferma prima della cancellazione, senza dipendere solo dal long press/context menu.</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>dive_detail_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>Azione distruttiva con conferma e feedback haptic; preserva stile dark/neon.</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Depth diagnostics row</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>Info mostra entitlement profondita configurato, disponibilita sensore, stato callback acqua e avviso che serve validazione Apple Watch Ultra reale.</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>settings_from_workflow.png; info_battery_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>Configurazione non equivale a certificazione o validazione hardware.</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>Inspectable sync queue controls</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>Settings mostra pending, sent, delivered/acknowledged, failed, last retry, retry e clear failed queue con conferma per la coda locale WatchConnectivity.</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>settings_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>Il direct send conserva pending finche iPhone non risponde con ack; transferUserInfo resta sent/ack pending finche non arriva conferma production.</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>GPS fix-source metadata</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>Le sessioni persistono se entry/exit GPS sono fix reale, fallback ultimo punto noto o no-fix.</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>gps_start_wait_from_workflow.png; gps_end_registered_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>GPS resta surface-only; nessun tracking subacqueo.</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Images</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>UserImages empty state</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>Se non esistono asset bundled, UserImages mostra stato vuoto esplicito invece di righe placeholder release-looking.</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>image_browser_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>Feature utile solo quando Resources/UserImages contiene asset reali.</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Watch post-fix compile blocker</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>`AscentWarningView` usa `Formatters.zero`; il formatter zero-decimal Watch e stato aggiunto senza modificare `Formatters.time` o `Formatters.one`.</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_BRANCHES_UX_INTERACTION_AUDIT_20260518_POST_FIX_PRE_MODIFICATION.md</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>Commit 946d3c1; resta da validare con xcodegen/xcodebuild su macOS.</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Logbook</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic month grouping</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>Logbook raggruppa le sessioni per mese/anno reale con label italiane invece di heading hardcoded.</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>ios_logbook_reference.png</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>Supporta sessioni importate e sincronizzate.</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>Analisi</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Sync Watch / iCloud / import CSV (empty state)</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>Empty state della tab Analisi separa Sync Watch da Sync iCloud e mantiene Importa CSV / Impostazioni come azioni reali.</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>Sostituisce copy legacy «Explore»; allineato a tab a cinque voci su `main`.</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Analisi</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>Empty-state direct actions (metriche)</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>La tab Analisi mostra azioni Importa CSV, Sync Watch e Apri Logbook quando non esistono dati analizzabili.</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>Usa dati reali; nessun placeholder analytics.</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Watch trust reset/re-pair</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>Settings espone peer verification state, ultimo sync e reset/re-pair con conferma, senza fallback trust deterministico.</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>Payload non verificati non sono presentati come sicuri.</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>Authorization status</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>Settings legge e mostra stato Authorized/Denied/Not determined/Provisional/Ephemeral e apre Impostazioni iOS.</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>Non richiede autorizzazione in-app in questo pass.</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Cloud merge-policy visibility</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>Settings documenta policy merge cloud/logbook, mostra preview locale/cloud/risultato scelto e dichiara i limiti last-write per planner/equipment.</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>Non promette conflict resolver per-campo; QA multi-device resta richiesto.</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Quoted CSV parser and partial summary</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>Import CSV gestisce campi quotati, righe vuote/malformed, duplicati, righe saltate e stato data sorgente preservata.</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>Aggiungere validazione bounds GPS/depth/duration prima release.</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Gear</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>Auto-save feedback</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>Gear mostra feedback discreto `Salvato` dopo auto-save/reset profilo.</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>Feedback minimale, stile premium dark.</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>Planner post-fix compile blocker</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>`PlannerView.swift` chiude correttamente `ResultPanelStyle` e mantiene `PlanTab` a file scope; Planner e PlanResult restano raggiungibili.</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_BRANCHES_UX_INTERACTION_AUDIT_20260518_POST_FIX_PRE_MODIFICATION.md</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>Commit 33bcb7e; resta da validare con xcodegen/xcodebuild su macOS.</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>TTV non-safety copy</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>Il label TTV resta visibile ma viene descritto come metrica informativa derivata da profondita media e runtime, non NDL/TTS/decompressione.</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>Non modifica calcolo esistente; solo copy/accessibility/documentazione.</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>Metric-only Watch units</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>L'opzione imperiale Watch non e selezionabile finche la conversione Watch non e implementata; export resta metrico/Subsurface.</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>settings_from_workflow.png</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>Evita selezione ft che mostrerebbe ancora dati metrici.</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>CSV bounds hardening</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Import CSV valida durata, profondita, temperatura e range GPS, preserva data sorgente e continua a gestire campi quotati e righe malformed.</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>Righe unrealistic vengono scartate/contate; test file reali ancora richiesti.</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Unknown values and chart accessibility</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>SAC, temperatura e accuratezza GPS mancanti usano `—` o `Non disponibile`; chart e controlli custom hanno label/sommari VoiceOver.</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>Non crea valori misurati finti.</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Subsurface</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>GPS fix-source export context</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>CSV export iOS include fix source entry/exit oltre alle coordinate, mantenendo GPS surface-only e distinguendo fix/fallback/no-fix.</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>Compatibilita Subsurface da verificare con import manuale.</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>PR #8 merge status</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>PR Update experimental Apnea workflow e conflittuale e con build check falliti.</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>GitHub PR #8</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>Non safe-to-merge automaticamente; richiede risoluzione conservativa e QA hardware. Sync 2026-05-19: mergeable=CONFLICTING, mergeStateStatus=DIRTY.</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>PR #9 merge status</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>PR Add experimental Apnea companion review e conflittuale e con build check falliti.</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>GitHub PR #9</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>Non safe-to-merge automaticamente; richiede risoluzione conservativa e QA iOS/macOS. Sync 2026-05-19: mergeable=CONFLICTING, mergeStateStatus=DIRTY.</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>BUILD_VALIDATION.md</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>Comandi documentati xcodegen + xcodebuild per scheme Watch/iOS e destinazioni generiche.</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>Docs/BUILD_VALIDATION.md</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-19; esecuzione solo su macOS.</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>GLOSSARY.md</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>Glossario utente TTV/TTR/SAC/MOD/GPS con mapping Watch-iOS-README.</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>Docs/GLOSSARY.md</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>Solo testo; non modifica calcoli.</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>RELEASE_CHECKLIST.md</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>Checklist release con matrice device, GPS negato, iCloud assente, export fallito.</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>Docs/RELEASE_CHECKLIST.md</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>Manuale.</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>UI_UX_VISUAL_GUIDELINES.md</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>Linee guida visive e path screenshot ReferenceUI.</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>Docs/UI_UX_VISUAL_GUIDELINES.md</t>
+        </is>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-19.</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_UX_COMPLETION_REPORT.md</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>Report pass UI/UX/safety senza business logic.</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>Docs/MAIN_UX_COMPLETION_REPORT.md</t>
+        </is>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-19.</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>IOS_TAB_TARGET_MISMATCH_REPORT.md</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>Analisi mismatch tab iOS vs target XcodeGen.</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>Docs/IOS_TAB_TARGET_MISMATCH_REPORT.md</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>Riferimento storico/fix.</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>Tab bar a cinque voci (2026-05)</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>Logbook, Analisi, Planner, Attrezzatura, Altro — route GPS in Analisi senza tab Explore separata.</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png; Docs/ReferenceUI/iOS_Companion_reference.png</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>Sostituisce descrizione legacy Route Review come tab dedicata.</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_SYNC_REPORT_20260519.md</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>Report A–K ispezione branch/PR e file documentali aggiornati.</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_SYNC_REPORT_20260519.md</t>
+        </is>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>Nessun merge PR automatico.</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_BRANCH_ALIGNMENT_20260519.md</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>Allineamento documentazione post-fetch origin.</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_BRANCH_ALIGNMENT_20260519.md</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>Aggiuntivo.</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>CHANGELOG.md root</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>Registro modifiche documentazione e release note sintetiche.</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>CHANGELOG.md</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>Avviato 2026-05-19.</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>CONTRIBUTING.md</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>Linee guida contribuzione documentazione e vincoli no-business-logic.</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>CONTRIBUTING.md</t>
+        </is>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-19.</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>Ritorno al punto di ingresso (Return-to-entry)</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>Navigazione verso il punto di partenza della sessione snorkeling (live + mappa ritorno dedicata), coerente con GPS di superficie e bearing UI.</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>03_Mappa_Ritorno_reference.png; Docs/SNORKELING_EXPERIMENTAL_SPEC.md</t>
+        </is>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>Non confondere con bussola Diving MAIN; terminologia UI: BUSSOLA / bearing waypoint.</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Snorkeling</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>Waypoint e bearing workflow</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>Selezione waypoint, dial bearing dedicato e marker POI con conferma; workflow documentato in specifica snorkeling.</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>04_Direzione_Waypoint_reference.png; gps_marker_style_reference.png</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>Sperimentale; sync iPhone boundary TODO dove indicato.</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_UPDATE_REPORT_20260519.md</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>Report strutturato post-pass documentazione (A–K), branch backup, PR GitHub.</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_UPDATE_REPORT_20260519.md</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; nessun merge PR automatico.</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>IOS_TAB_TARGET_MISMATCH_STATUS</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>Stato mismatch tab iOS vs `project.yml` e checklist Definition of Done.</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>Docs/IOS_TAB_TARGET_MISMATCH_STATUS_20260519.md</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>HEAD vs working tree: vedi sezione 1 del file.</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>Selettore lingua app (System/IT/EN)</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>`DIRAppLanguage` con `@AppStorage` e `.environment(\.locale, ...)` sulla WindowGroup; picker in `SettingsView`.</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>App/DIRAppLanguage.swift; Views/SettingsView.swift</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>Locale Watch indipendente da iPhone (sandbox UserDefaults separati).</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>it, en, system (fallback it se sistema non it/en)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>Selettore lingua app (System/IT/EN)</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>`DIRIOSAppLanguage` con `@AppStorage` e `.environment(\.locale, ...)` sulla WindowGroup; picker in `MoreView`.</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/App/DIRIOSAppLanguage.swift; iOSApp/Views/MoreView.swift</t>
+        </is>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>Modifica lingua non cambia unita, calcoli, persistenza o dati salvati.</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>it, en, system (fallback it se sistema non it/en)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Tabelle stringhe Watch</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>`Localizable.strings` en/it con chiavi settings, live dive, logbook, compass, more, analisi.</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>Resources/en.lproj/Localizable.strings; Resources/it.lproj/Localizable.strings</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>~89 chiavi EN; copertura parziale finche restano `Text(\\")` letterali."</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>Aggiunta chiave accessibility.command_button.hint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>Tabelle stringhe iOS</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>`Localizable.strings` en/it con chiavi tab.*, preferenze, sync, planner.</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/Resources/en.lproj/Localizable.strings; iOSApp/Resources/it.lproj/Localizable.strings</t>
+        </is>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>~58+ chiavi EN; copertura parziale.</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>Aggiunte chiavi tab.* e logbook.delete.a11y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Logbook locale-aware</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>Intestazioni mese e abbreviazione mese su `DiveLogCard` usano `@Environment(\\.locale)` invece di `it_IT` fisso.</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/Views/LogbookView.swift</t>
+        </is>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>Commit 4cca72e; nessuna modifica a logica.</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>Segue lingua app via Locale ambientale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Hint VoiceOver comandi</t>
+        </is>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>`DiveCommandButton` usa `LocalizedStringKey` per label e hint; chiave `accessibility.command_button.hint` in EN/IT.</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>Views/DiveUIComponents.swift</t>
+        </is>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>Commit 4cca72e.</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>Hint coerente con lingua app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>Migrazione stringhe residue</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>Molte viste usano ancora `Text(\...\")` letterali italiani; con lingua=EN restano in italiano finche non chiavate."</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>Da pianificare migrazione progressiva (eventuale `.xcstrings`).</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>Coverage gap noto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>Sync preferenza lingua Watch &lt;-&gt; iPhone</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>UserDefaults sandbox separati: cambio lingua su un dispositivo non si propaga.</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>Eventuale WatchConnectivity context per allineare preferenza.</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>Roadmap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_UPDATE_REPORT_20260519_I18N.md</t>
+        </is>
+      </c>
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>Report strutturato A-K post-pass i18n e allineamento branch matrix.</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_UPDATE_REPORT_20260519_I18N.md</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; nessun merge PR automatico.</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>Audit di sicurezza A-K (18 finding)</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>Audit statico su auth/sync/crypto/persistence/network/entitlements/privacy. 2 HIGH, 4 MEDIUM, 6 LOW, 6 INFO; remediation F1-F12 applicate.</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>Docs/SECURITY_AUDIT_MAIN_AND_MAIN_IOS_20260519.md</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>Commit c9b9802 (audit) + 4136ec0 (fix).</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>Lingua audit IT/EN tecnico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>F1 - WatchSyncAuth.resetPeerTrust</t>
+        </is>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>Ripristinato reset associazione Watch su iOS MAIN con helper `deleteKeychain(account:service:)`.</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/Services/WatchSyncAuth.swift</t>
+        </is>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>Build break su main risolto.</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>UI italiano: `Trust Watch resettato`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>F2 - syncKey v2 ordered-secrets</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>Algoritmo HMAC autoritativo documentato con commento MARK su entrambi WatchSyncAuth.swift; cambio futuro richiede bump schemaVersion.</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>Services/WatchSyncAuth.swift; iOSApp/Services/WatchSyncAuth.swift</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>Algoritmo: SHA256(\dirdiving.watch.sync.v2|...|\" || sort_lex(localSecret</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> peerSecret))."</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>F3 - Watch CSV export Data Protection</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>Export Subsurface ora `[.atomic, .completeFileProtection]`, UUID filename e cleanup 24h.</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>Services/SubsurfaceExportService.swift</t>
+        </is>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>Formato CSV business invariato (header/ordine colonne).</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>F6 - Replay window 1h</t>
+        </is>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>`WatchDiveSyncCodec.maxIssuedAtSkew` ridotto da 86400s a 3600s.</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/Services/WatchDiveSyncCodec.swift</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>Pairing-locked al livello OS; finestra ridotta come difesa-in-profondita.</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>F7 - No deterministic secret fallback</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>`loadOrCreateLocalSecret` ora `Data?`; SecRandomCopyBytes failure non genera piu un secret pubblico deterministico.</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>Services/WatchSyncAuth.swift; iOSApp/Services/WatchSyncAuth.swift</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>Logging via os.Logger con privacy:.private.</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>F8 - Naming canonical dirdiving_*</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>Nuove costanti `dirdiving_*` (Keychain iOS, Notification.Name, AscentRateSettingsStore) con read-fallback dal legacy `dirmotion_*`.</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>Services/AscentRateSettingsStore.swift; Utils/WatchSyncNotifications.swift; iOSApp/Services/WatchSyncAuth.swift</t>
+        </is>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>Migrazione one-shot; nessuna chiave persistita rimossa direttamente.</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>F9 - Pending/conflicts -&gt; Documents protected</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>Pending sessions Watch e conflicts iOS migrati da UserDefaults a `Documents/*.json` con `.completeFileProtection`.</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>Services/WatchSyncService.swift; iOSApp/Services/WatchSyncService.swift</t>
+        </is>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>Migrazione una tantum; legacy UserDefaults key rimossa post-migrate.</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>F10 - CSV import size cap 10 MB</t>
+        </is>
+      </c>
+      <c r="F141" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>Pre-check via `URLResourceValues.fileSize` + post-check UTF-8 bytes; nuovo errore `.fileTooLarge`.</t>
+        </is>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/Services/DiveImportService.swift</t>
+        </is>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>Messaggio UI: `CSV troppo grande: limite 10 MB.`</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>Errore localizzato IT; chiave EN da aggiungere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>F11 - Signed WatchConnectivity ack</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>Ack HMAC su `\ack|sessionID|issuedAt\"`; verify constant-time lato Watch."</t>
+        </is>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>Services/WatchDiveSyncCodec.swift; iOSApp/Services/WatchDiveSyncCodec.swift</t>
+        </is>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>Fallback legacy `status == acknowledged` mantenuto per backward compat; TODO follow-up rimuovere quando floor build sale.</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>F12 - Logger sostituisce print</t>
+        </is>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>`Logger(subsystem: \com.egopfe.dirdiving\"</t>
+        </is>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> category: \"DiveLogStore\")` con `privacy:.private` su dettagli errore."</t>
+        </is>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>Services/DiveLogStore.swift</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="inlineStr">
+        <is>
+          <t>Nessun GPS/session content esposto in console/sysdiagnose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>F11-followup - Mandatory signed ack</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>Quando il floor build iOS sale, trattare il path legacy `status == acknowledged` come `failed`.</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>Allineamento release Watch + iOS richiesto.</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>F4/F5 regressioni vs main</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>Su origin/main-iOS: rimozione `.completeFileProtection`/cleanup nell'export e bound di import CSV. Bloccare merge verso MAIN.</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/Services/SubsurfaceExportService.swift; iOSApp/Services/DiveImportService.swift</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>Da riallineare prima di unificare main-iOS in main.</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_UPDATE_REPORT_20260519_SECURITY.md</t>
+        </is>
+      </c>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>Report A-K post-pass documentazione security (file aggiornati, branch, PR, gap).</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_UPDATE_REPORT_20260519_SECURITY.md</t>
+        </is>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; nessun merge PR automatico.</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>RELEASE_CHECKLIST.md QA Security</t>
+        </is>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>Sezione QA Security F1-F12 aggiunta al release checklist: auth/pairing, Data Protection, sync protocol, input validation, logging, privacy/leakage.</t>
+        </is>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>Docs/RELEASE_CHECKLIST.md</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>Additivo; checklist documentale (non runtime).</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>Chiavi import.csv.* (F10 follow-up)</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>Chiavi `import.csv.too_large`, `.too_large.10mb`, `.unreadable`, `.missing_columns`, `.empty_profile` pre-pubblicate in EN/IT in Localizable.strings; runtime in DiveImportService.swift restituisce ancora IT hardcoded.</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>iOSApp/Resources/en.lproj/Localizable.strings; iOSApp/Resources/it.lproj/Localizable.strings</t>
+        </is>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>Follow-up: passaggio a NSLocalizedString in DiveImportService.ImportError.errorDescription.</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>it, en (formato %d MB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_UPDATE_REPORT_20260519_SECURITY_PT2.md</t>
+        </is>
+      </c>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>Report A-K post-pass docs security PT2 (release checklist + i18n keys gap).</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_UPDATE_REPORT_20260519_SECURITY_PT2.md</t>
+        </is>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione.</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_PRE_RELEASE_OPEN_ITEMS_20260519.md</t>
+        </is>
+      </c>
+      <c r="F150" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>Backlog rimanente / item rinviati post pre-release pass: Watch imperial conversion, GPX/UDDF, per-field cloud merge per Equipment/Planner, side-button capture watchOS, convergenza branch.</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>Docs/MAIN_PRE_RELEASE_OPEN_ITEMS_20260519.md</t>
+        </is>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; nessun commit business logic in questo pass.</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_PRE_RELEASE_SIMULATOR_QA_20260519.md</t>
+        </is>
+      </c>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>Checklist QA eseguibile pre-release per Watch Ultra/piccolo e iPhone SE/Pro Max: UX-H1..H4, SAF-3..SAF-10, App Intents, haptics matrix, a11y, Dynamic Type.</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>Docs/MAIN_PRE_RELEASE_SIMULATOR_QA_20260519.md</t>
+        </is>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>Richiede installazione platform runtime iOS 26.5/watchOS 26.5 per full xcodebuild; comandi documentati nel file.</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>UX-H1/SAF-6 - Tombstone unified key</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>Chiave deleted-session unificata `dirdiving_shared_deleted_session_ids` Watch+iOS per evitare resurrezione cross-device.</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>Implementato su backup branch; in attesa riconciliazione con security F1-F12 in `Services/WatchSyncService.swift`.</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>UX-H2 - Watch consumer side iOS push</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>Watch accetta payload iOS firmati HMAC tramite `WatchDiveSyncCodec.parseSession` + `WatchSyncService.attachLogStore`; previene loop sync.</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>Implementato su backup branch; gated da `WatchSyncAuth.hasPeerSecret()`.</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>UX-H3/SAF-1 - Ascent warning preserves gauge</t>
+        </is>
+      </c>
+      <c r="F154" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>Banner inline `AscentWarningBannerView` tra TTV/RunTime e depth; nessun full-screen takeover; gauge sempre visibile.</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>ascent_alarm.png; Views/AscentWarningBannerView.swift</t>
+        </is>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20 su main; sostituisce policy 1 s full-screen del backup backlog.</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>it, en ascent_alarm_* keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>UX-H4/SAF-2 - GPS confirmation compact banner</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>Conferma GPS start/end ora banner top compatto (verde/giallo) invece di full-screen; depth e gauge restano visibili.</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>Implementato su backup branch; preserva semantiche `no-fix` / `fallback`.</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>UX-H5 - Canonical iOS branch documented</t>
+        </is>
+      </c>
+      <c r="F156" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>`Docs/IOS_COMPANION_MAIN_CANONICAL_NOTE.md` su `main-iOS` dichiara `main-iOS` canonico per iOS; `main` mantiene `iOSApp/` legacy per build unificato.</t>
+        </is>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>Docs/IOS_COMPANION_MAIN_CANONICAL_NOTE.md</t>
+        </is>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>Convergenza strutturale rimanda a post-release (vedi Open Items).</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>UX-M1/M3 - ModeSelection drop + UserImages conditional</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>`Models/AppPage.swift` rimuove `.modeSelection`; `ContentView` rende UserImages solo se assets bundled.</t>
+        </is>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>README aggiornato post-merge.</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>UX-M4/M5/M8 - Sync retry + bearing toast + info-rows</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>`SettingsView` con `infoRow/statusRow/settingsRow`; retry sempre visibile (disabled quando idle); CompassView mostra toast `Bearing impostato`.</t>
+        </is>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>Tutte modifiche additive UI; nessuna business logic toccata.</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>UX-L1/L2/L5/L6/L8/L9 - LOW cluster</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>ExportView copy `FILE CSV PRONTO`; units pill metric-only; CLEAR disabled visible; a11y labels su DiveLive/Detail/Compass/Alarm; alarm step copy; single delete path.</t>
+        </is>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>Vincoli a11y allineati a UX-L6; nessuna modifica funzionale.</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>SAF-3 - TTV INFO visual de-emphasis</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>DiveLiveView TTV mostrato come `TTV INFO` in `DiveUI.secondaryText` + a11y hint che chiarisce nature informativa, non NDL/time-to-surface.</t>
+        </is>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>Algoritmo TTV invariato; solo display + accessibility.</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
+        <is>
+          <t>SAF-7 - Haptics-off badge pre-dive</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>Badge `APTICA DISATTIVATA / AVVISI SOLO VISIVI` ora reso anche nello stato pre-dive, non solo in-water.</t>
+        </is>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I161" s="9" t="inlineStr">
+        <is>
+          <t>Helps awareness prima dell'ingresso in acqua.</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>SAF-8 - Alarm acknowledge with cooldown</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>Banner alarm Watch espone bottone `OK` che chiama `dive.dismissAlarmWarning`; AcknowledgeAlarmIntent App Intent aggiunto.</t>
+        </is>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>Cooldown gestito da DiveManager; soglie alarm invariate.</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr">
+        <is>
+          <t>SAF-10 - Per-session sync delivery TODO honest</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>Settings Watch e MoreView iOS espongono riga `Delivery per log: TODO: stato per-sessione planned` invece di lasciare ambiguita.</t>
+        </is>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>Views/SettingsView.swift; iOSApp/Views/MoreView.swift</t>
+        </is>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>Migrazione a status per-session.id rimanda a post-release.</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>Phase-5 App Intents</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>Pending merge</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>`Services/ActionButtonIntents.swift` aggiunge `StartManualDiveIntent`, `EndManualDiveIntent`, `SetBearingIntent`, `ClearBearingIntent`, `AcknowledgeAlarmIntent`.</t>
+        </is>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>backup/main-watch-backlog-20260519</t>
+        </is>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>Nessun side-button watchOS reclamato; copy in WatchShortcutHelpView esplicita il limite OS.</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_UPDATE_REPORT_20260519_PRE_RELEASE_BACKLOG.md</t>
+        </is>
+      </c>
+      <c r="F165" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>Report A-K post-pass pre-release backlog: branch ispezionati, file modificati, PR analizzate, gap residue, rischi.</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_UPDATE_REPORT_20260519_PRE_RELEASE_BACKLOG.md</t>
+        </is>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; nessun merge automatico di PR.</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
+        <is>
+          <t>WATCH_MAIN_UX_CONVENTIONS.md</t>
+        </is>
+      </c>
+      <c r="F166" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>Baseline UX Watch MAIN: banner risalita inline non bloccante; Mode Selection accettata su launch.</t>
+        </is>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>Docs/WATCH_MAIN_UX_CONVENTIONS.md</t>
+        </is>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20; product policy per future UI.</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>ASCENT_ALARM_IMPLEMENTATION_REPORT_20260520.md</t>
+        </is>
+      </c>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>Report implementazione banner risalita: file, haptic, i18n, QA checklist.</t>
+        </is>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>Docs/ASCENT_ALARM_IMPLEMENTATION_REPORT_20260520.md</t>
+        </is>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>Nessuna modifica soglie risalita.</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="inlineStr">
+        <is>
+          <t>it, en keys documentate nel report</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E168" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_BRANCHES_UX_INTERACTION_AUDIT_20260519</t>
+        </is>
+      </c>
+      <c r="F168" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr">
+        <is>
+          <t>Audit UX/interaction/feature accessibility Watch+iOS MAIN pre-modifica; .md + .docx.</t>
+        </is>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>Docs/MAIN_BRANCHES_UX_INTERACTION_AUDIT_20260519_CURRENT_PRE_MODIFICATION.md</t>
+        </is>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>Nota 2026-05-20: policy risalita superseded da banner inline su main.</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_UPDATE_REPORT_20260520.md</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>Report A-K pass documentazione post-banner risalita e allineamento branch matrix.</t>
+        </is>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_UPDATE_REPORT_20260520.md</t>
+        </is>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; PR #8/#9 non merge automatico.</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_BRANCH_ALIGNMENT_20260520.md</t>
+        </is>
+      </c>
+      <c r="F170" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>Allineamento documentazione dopo fetch origin; stato branch e gap residue.</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_BRANCH_ALIGNMENT_20260520.md</t>
+        </is>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>Aggiuntivo.</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>Secondary i18n pass 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="inlineStr">
+        <is>
+          <t>~130+ Watch + ~90+ iOS string keys; services sync/compass/alarm localized at assignment.</t>
+        </is>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>Resources/*.lproj; iOSApp/Resources/*.lproj</t>
+        </is>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>Uncommitted then commit on main; status messages refresh on next sync event after language change.</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="inlineStr">
+        <is>
+          <t>it, en via DIRAppLanguage/DIRIOSAppLanguage</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>Diving</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>P0 Watch inbound WCSession consumer</t>
+        </is>
+      </c>
+      <c r="F172" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G172" s="9" t="inlineStr">
+        <is>
+          <t>didReceiveMessage/UserInfo; ingestIncomingPayload; tombstone via applicationContext.</t>
+        </is>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>Services/WatchSyncService.swift</t>
+        </is>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>Commit a75a6c3; security F9/F11 preserved.</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="inlineStr">
+        <is>
+          <t>it, en sync.* strings</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>SAFETY_DISCLAIMER.md + TESTFLIGHT_REVIEW_NOTES.md</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>Disclaimer IT + note reviewer TestFlight.</t>
+        </is>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>Docs/SAFETY_DISCLAIMER.md; Docs/TESTFLIGHT_REVIEW_NOTES.md</t>
+        </is>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20 docs pass.</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>ROADMAP.md</t>
+        </is>
+      </c>
+      <c r="F174" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>Roadmap MAIN vs experimental.</t>
+        </is>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>Docs/ROADMAP.md</t>
+        </is>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>Additive.</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="inlineStr">
+        <is>
+          <t>MAIN_ISSUES_IMPLEMENTATION_REPORT_20260520</t>
+        </is>
+      </c>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>Report A-O post P0/P1/P2 implementation.</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>Docs/MAIN_ISSUES_IMPLEMENTATION_REPORT_20260520.md</t>
+        </is>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>Backlog manual port not cherry-pick.</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_BRANCH_ALIGNMENT_20260522.md</t>
+        </is>
+      </c>
+      <c r="F176" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>Report A-K post-fetch 2026-05-22: branch, worktree, PR #8/#9, conflitti docs risolti e main-iOS lasciato a review manuale.</t>
+        </is>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_BRANCH_ALIGNMENT_20260522.md</t>
+        </is>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; nessuna modifica deliberata a GPS, BUSSOLA, calcoli o persistenza.</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>PR status verification 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F177" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G177" s="9" t="inlineStr">
+        <is>
+          <t>PR #8 e #9 verificate con gh: entrambe CONFLICTING/DIRTY e non safe-to-merge automatico.</t>
+        </is>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>Docs/PR_STATUS_20260520.md</t>
+        </is>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>Worktree experimental fast-forwardati ai remote; nessun merge PR eseguito.</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>Branching</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>Companion</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS divergence review</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS local ahead 2 / behind 10; merge preview mostra conflitti docs e runtime iOS da risolvere in pass dedicato.</t>
+        </is>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_BRANCH_ALIGNMENT_20260522.md</t>
+        </is>
+      </c>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>Non risolto automaticamente per evitare modifiche a import CSV, sync, planner o persistenza.</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>First launch</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>Legal onboarding and disclaimer acceptance</t>
+        </is>
+      </c>
+      <c r="F179" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G179" s="9" t="inlineStr">
+        <is>
+          <t>Flusso Welcome, Safety Warning, Legal Disclaimer e Acceptance prima della ContentView; re-consent su major version/legal revision.</t>
+        </is>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>Persistenza UserDefaults: timestamp, versione, major, device type, lingua e legal revision; nessuna modifica a telemetry/GPS/BUSSOLA/calcoli.</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="inlineStr">
+        <is>
+          <t>it, en; segue DIRAppLanguage system/it/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>First launch</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="inlineStr">
+        <is>
+          <t>Legal onboarding and disclaimer acceptance</t>
+        </is>
+      </c>
+      <c r="F180" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G180" s="9" t="inlineStr">
+        <is>
+          <t>Flusso premium iOS prima della tabbar companion con warning NOT A DIVE COMPUTER, disclaimer scrollabile e checkbox obbligatorie.</t>
+        </is>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>Dark mode, card premium, gating non bypassabile salvo reset dati app; nessuna modifica a planner/sync/export.</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="inlineStr">
+        <is>
+          <t>it, en; segue DIRIOSAppLanguage system/it/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>codex/experimental-features</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>First launch</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>Legal onboarding and disclaimer acceptance</t>
+        </is>
+      </c>
+      <c r="F181" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>Stesso gating legale del Watch main applicato al branch experimental mantenendo isolate Snorkeling/Apnea/Buddy.</t>
+        </is>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>Le feature experimental restano lab/experimental dopo accettazione; non diventano safety-certified.</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="inlineStr">
+        <is>
+          <t>it, en</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>codex/ios-experimental-features</t>
+        </is>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>First launch</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
+          <t>Legal onboarding and disclaimer acceptance</t>
+        </is>
+      </c>
+      <c r="F182" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="inlineStr">
+        <is>
+          <t>Stesso gating legale iOS applicato al companion experimental senza promuovere Explore/Buddy/Apnea lab a stable.</t>
+        </is>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>UI premium iOS; feature experimental marcate come tali.</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="inlineStr">
+        <is>
+          <t>it, en</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E183" s="9" t="inlineStr">
+        <is>
+          <t>Legal &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F183" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>Schermata Settings dedicata con NOT A DIVE COMPUTER, versione accettata, timestamp, lingua, disclaimer completo e link Terms/Privacy.</t>
+        </is>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE_DIVING_LIVE.png</t>
+        </is>
+      </c>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
+          <t>Aggiunta solo UI/settings; non altera workflow immersione.</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="inlineStr">
+        <is>
+          <t>it, en</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>main-iOS</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="E184" s="9" t="inlineStr">
+        <is>
+          <t>Legal &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F184" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="inlineStr">
+        <is>
+          <t>Sezione More/Settings con log accettazione, disclaimer completo e link Terms/Privacy.</t>
+        </is>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>iOS_look_feel.png</t>
+        </is>
+      </c>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>Aggiunta nel pannello PREFERENZE APP; mantiene tabbar e sync invariati.</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="inlineStr">
+        <is>
+          <t>it, en</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch + iOS</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
+          <t>Localized full legal disclaimer resources</t>
+        </is>
+      </c>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>Disclaimer completo estratto dai DOCX legali in LegalDisclaimer.txt per en.lproj/it.lproj su Watch e iOS.</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>DIR_Diving_Complete_Disclaimer_ENG.docx; DIR_Diving_Complete_Disclaimer_ITA.docx</t>
+        </is>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>CSV/XLSX documentano la disponibilita lingue; contenuto legale va rivisto prima release se cambiano documenti sorgente.</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>Italiano, English</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E186" s="9" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION_UPDATE_REPORT_20260522_LEGAL_ONBOARDING.md</t>
+        </is>
+      </c>
+      <c r="F186" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G186" s="9" t="inlineStr">
+        <is>
+          <t>Report A-K per update documentale post onboarding legale, branch matrix e PR status.</t>
+        </is>
+      </c>
+      <c r="H186" s="9" t="inlineStr">
+        <is>
+          <t>Docs/DOCUMENTATION_UPDATE_REPORT_20260522_LEGAL_ONBOARDING.md</t>
+        </is>
+      </c>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>Solo documentazione; nessuna modifica runtime.</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>XcodeGen</t>
+        </is>
+      </c>
+      <c r="E187" s="9" t="inlineStr">
+        <is>
+          <t>Project structure unchanged after docs pass</t>
+        </is>
+      </c>
+      <c r="F187" s="10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>project.yml ispezionato: scheme DIRDiving Watch App e DIRDiving iOS invariati; build reale richiesta su macOS.</t>
+        </is>
+      </c>
+      <c r="H187" s="9" t="inlineStr">
+        <is>
+          <t>project.yml; Docs/BUILD_VALIDATION.md</t>
+        </is>
+      </c>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>Ambiente Windows non dispone di xcodegen/xcodebuild/swift; validazione Apple demandata a macOS.</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>Pull Requests</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="inlineStr">
+        <is>
+          <t>PR #8</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
+        <is>
+          <t>Experimental merge</t>
+        </is>
+      </c>
+      <c r="E188" s="9" t="inlineStr">
+        <is>
+          <t>Update experimental Apnea workflow</t>
+        </is>
+      </c>
+      <c r="F188" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G188" s="9" t="inlineStr">
+        <is>
+          <t>PR aperta codex/experimental-features -&gt; main; GitHub mergeable CONFLICTING e build check failure.</t>
+        </is>
+      </c>
+      <c r="H188" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/egopfe/DirDiving-App/pull/8</t>
+        </is>
+      </c>
+      <c r="I188" s="9" t="inlineStr">
+        <is>
+          <t>Non mergeare automaticamente; preservare Diving, BUSSOLA, GPS surface-only e project.yml experimental exclusions.</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>Pull Requests</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>PR #9</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>iOS</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>Experimental merge</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>Add experimental Apnea companion review</t>
+        </is>
+      </c>
+      <c r="F189" s="12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr">
+        <is>
+          <t>PR aperta codex/ios-experimental-features -&gt; main-iOS; GitHub mergeable CONFLICTING e build check failure.</t>
+        </is>
+      </c>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/egopfe/DirDiving-App/pull/9</t>
+        </is>
+      </c>
+      <c r="I189" s="9" t="inlineStr">
+        <is>
+          <t>Non mergeare automaticamente; richiede review regressioni iOS e isolamento experimental.</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J189"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2410,4 +11805,70 @@
   <autoFilter ref="A6:G54"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="7" min="1" max="1"/>
+    <col width="120" customWidth="1" style="7" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Docs/DIR_DIVING_Feature_Comparison.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Legal onboarding/disclaimer acceptance, branch matrix, PR status, UI/UX docs alignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Runtime constraint</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Documentation-only workbook update; no app logic changes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>